--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T06:07:49+00:00</t>
+    <t>2023-11-14T21:40:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from DDCC Codes for I" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from mms" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>WHO_DDCC_Test_Result_COVID_19</t>
+    <t>WHODDCCTestResultCOVID19</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T00:11:34+00:00</t>
+    <t>2024-07-30T07:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>WHO (http://who.int)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-who-ddcc-test-result-covid-19.xlsx
+++ b/ValueSet-who-ddcc-test-result-covid-19.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-30T07:55:09+00:00</t>
+    <t>2024-07-30T11:13:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
